--- a/SeleniumTests/Import Transaction/With Data/invoice_template.xlsx
+++ b/SeleniumTests/Import Transaction/With Data/invoice_template.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29426"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ChooYanShen\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\e-invoice\SeleniumTests\Import Transaction\With Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AD435629-5267-4099-A0BC-DB22FE070E0C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A75DA617-0779-4F70-9C25-479B207FEDCB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Transaction" sheetId="2" r:id="rId1"/>
@@ -467,13 +467,13 @@
     <t>1</t>
   </si>
   <si>
-    <t>2025-11-20</t>
-  </si>
-  <si>
-    <t>INV1110_V2_000001</t>
-  </si>
-  <si>
-    <t>INV1110_V2_000002</t>
+    <t>INV1217_V2_000001</t>
+  </si>
+  <si>
+    <t>INV1217_V2_000002</t>
+  </si>
+  <si>
+    <t>2025-12-17</t>
   </si>
 </sst>
 </file>
@@ -1528,13 +1528,13 @@
         <v>134</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>135</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="G4" s="2" t="s">
         <v>136</v>
@@ -1676,13 +1676,13 @@
         <v>134</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>135</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="G5" s="2" t="s">
         <v>136</v>
